--- a/research/traditional_assets/database/data/jamaica/jamaica_insurance_life.xlsx
+++ b/research/traditional_assets/database/data/jamaica/jamaica_insurance_life.xlsx
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0866</v>
+        <v>0.0761</v>
       </c>
       <c r="E2">
-        <v>0.07719999999999999</v>
+        <v>0.0233</v>
       </c>
       <c r="G2">
-        <v>0.2450762624018955</v>
+        <v>0.282703488372093</v>
       </c>
       <c r="H2">
-        <v>0.2450762624018955</v>
+        <v>0.282703488372093</v>
       </c>
       <c r="I2">
-        <v>0.2511476380867763</v>
+        <v>0.2359893889325057</v>
       </c>
       <c r="J2">
-        <v>0.1779628964149927</v>
+        <v>0.1667449045228939</v>
       </c>
       <c r="K2">
-        <v>112.6</v>
+        <v>95.8</v>
       </c>
       <c r="L2">
-        <v>0.1667407078335555</v>
+        <v>0.1392441860465116</v>
       </c>
       <c r="M2">
-        <v>19.213</v>
+        <v>40.2</v>
       </c>
       <c r="N2">
-        <v>0.013001962509305</v>
+        <v>0.02648395810000659</v>
       </c>
       <c r="O2">
-        <v>0.1706305506216697</v>
+        <v>0.4196242171189979</v>
       </c>
       <c r="P2">
-        <v>18.3</v>
+        <v>40.2</v>
       </c>
       <c r="Q2">
-        <v>0.01238411044190296</v>
+        <v>0.02648395810000659</v>
       </c>
       <c r="R2">
-        <v>0.1625222024866785</v>
+        <v>0.4196242171189979</v>
       </c>
       <c r="S2">
-        <v>0.9130000000000003</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>0.04751990839535732</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>175.5</v>
+        <v>215.5</v>
       </c>
       <c r="V2">
-        <v>0.118765649319889</v>
+        <v>0.1419724619540154</v>
       </c>
       <c r="W2">
-        <v>0.156020507135929</v>
+        <v>0.1226475483292792</v>
       </c>
       <c r="X2">
-        <v>0.1133977178545365</v>
+        <v>0.1642152879541893</v>
       </c>
       <c r="Y2">
-        <v>0.04262278928139258</v>
+        <v>-0.04156773962491012</v>
       </c>
       <c r="Z2">
-        <v>1.073438245112065</v>
+        <v>0.9933848910800059</v>
       </c>
       <c r="AA2">
-        <v>0.1910321792227699</v>
+        <v>0.1656418688176209</v>
       </c>
       <c r="AB2">
-        <v>0.1103483982434059</v>
+        <v>0.1629238276653961</v>
       </c>
       <c r="AC2">
-        <v>0.080683780979364</v>
+        <v>0.002718041152224765</v>
       </c>
       <c r="AD2">
-        <v>86.7</v>
+        <v>28.4</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>0.2815020721804781</v>
       </c>
       <c r="AF2">
-        <v>86.7</v>
+        <v>28.68150207218047</v>
       </c>
       <c r="AG2">
-        <v>-88.8</v>
+        <v>-186.8184979278195</v>
       </c>
       <c r="AH2">
-        <v>0.05542060854001534</v>
+        <v>0.01854509577009145</v>
       </c>
       <c r="AI2">
-        <v>0.08633738299143597</v>
+        <v>0.03866048956884484</v>
       </c>
       <c r="AJ2">
-        <v>-0.06393548851609186</v>
+        <v>-0.1403509083681105</v>
       </c>
       <c r="AK2">
-        <v>-0.1071557861711114</v>
+        <v>-0.3549108340478915</v>
       </c>
       <c r="AL2">
-        <v>34.4</v>
+        <v>33.8</v>
       </c>
       <c r="AM2">
-        <v>34.4</v>
+        <v>33.8</v>
       </c>
       <c r="AN2">
-        <v>0.4803324099722992</v>
+        <v>0.1630150903757957</v>
       </c>
       <c r="AO2">
-        <v>4.930232558139535</v>
+        <v>4.795857988165681</v>
       </c>
       <c r="AP2">
-        <v>-0.4919667590027701</v>
+        <v>-1.072332194492039</v>
       </c>
       <c r="AQ2">
-        <v>4.930232558139535</v>
+        <v>4.795857988165681</v>
       </c>
     </row>
     <row r="3">
@@ -722,121 +722,121 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0866</v>
+        <v>0.0761</v>
       </c>
       <c r="E3">
-        <v>0.07719999999999999</v>
+        <v>0.0233</v>
       </c>
       <c r="G3">
-        <v>0.2450762624018955</v>
+        <v>0.282703488372093</v>
       </c>
       <c r="H3">
-        <v>0.2450762624018955</v>
+        <v>0.282703488372093</v>
       </c>
       <c r="I3">
-        <v>0.2511476380867763</v>
+        <v>0.2359893889325057</v>
       </c>
       <c r="J3">
-        <v>0.1779628964149927</v>
+        <v>0.1667449045228939</v>
       </c>
       <c r="K3">
-        <v>112.6</v>
+        <v>95.8</v>
       </c>
       <c r="L3">
-        <v>0.1667407078335555</v>
+        <v>0.1392441860465116</v>
       </c>
       <c r="M3">
-        <v>19.213</v>
+        <v>40.2</v>
       </c>
       <c r="N3">
-        <v>0.013001962509305</v>
+        <v>0.02648395810000659</v>
       </c>
       <c r="O3">
-        <v>0.1706305506216697</v>
+        <v>0.4196242171189979</v>
       </c>
       <c r="P3">
-        <v>18.3</v>
+        <v>40.2</v>
       </c>
       <c r="Q3">
-        <v>0.01238411044190296</v>
+        <v>0.02648395810000659</v>
       </c>
       <c r="R3">
-        <v>0.1625222024866785</v>
+        <v>0.4196242171189979</v>
       </c>
       <c r="S3">
-        <v>0.9130000000000003</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>0.04751990839535732</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>175.5</v>
+        <v>215.5</v>
       </c>
       <c r="V3">
-        <v>0.118765649319889</v>
+        <v>0.1419724619540154</v>
       </c>
       <c r="W3">
-        <v>0.156020507135929</v>
+        <v>0.1226475483292792</v>
       </c>
       <c r="X3">
-        <v>0.1133977178545365</v>
+        <v>0.1642152879541893</v>
       </c>
       <c r="Y3">
-        <v>0.04262278928139258</v>
+        <v>-0.04156773962491012</v>
       </c>
       <c r="Z3">
-        <v>1.073438245112065</v>
+        <v>0.9933848910800059</v>
       </c>
       <c r="AA3">
-        <v>0.1910321792227699</v>
+        <v>0.1656418688176209</v>
       </c>
       <c r="AB3">
-        <v>0.1103483982434059</v>
+        <v>0.1629238276653961</v>
       </c>
       <c r="AC3">
-        <v>0.080683780979364</v>
+        <v>0.002718041152224765</v>
       </c>
       <c r="AD3">
-        <v>86.7</v>
+        <v>28.4</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>0.2815020721804781</v>
       </c>
       <c r="AF3">
-        <v>86.7</v>
+        <v>28.68150207218047</v>
       </c>
       <c r="AG3">
-        <v>-88.8</v>
+        <v>-186.8184979278195</v>
       </c>
       <c r="AH3">
-        <v>0.05542060854001534</v>
+        <v>0.01854509577009145</v>
       </c>
       <c r="AI3">
-        <v>0.08633738299143597</v>
+        <v>0.03866048956884484</v>
       </c>
       <c r="AJ3">
-        <v>-0.06393548851609186</v>
+        <v>-0.1403509083681105</v>
       </c>
       <c r="AK3">
-        <v>-0.1071557861711114</v>
+        <v>-0.3549108340478915</v>
       </c>
       <c r="AL3">
-        <v>34.4</v>
+        <v>33.8</v>
       </c>
       <c r="AM3">
-        <v>34.4</v>
+        <v>33.8</v>
       </c>
       <c r="AN3">
-        <v>0.4803324099722992</v>
+        <v>0.1630150903757957</v>
       </c>
       <c r="AO3">
-        <v>4.930232558139535</v>
+        <v>4.795857988165681</v>
       </c>
       <c r="AP3">
-        <v>-0.4919667590027701</v>
+        <v>-1.072332194492039</v>
       </c>
       <c r="AQ3">
-        <v>4.930232558139535</v>
+        <v>4.795857988165681</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/jamaica/jamaica_insurance_life.xlsx
+++ b/research/traditional_assets/database/data/jamaica/jamaica_insurance_life.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0761</v>
+        <v>0.092</v>
       </c>
       <c r="E2">
-        <v>0.0233</v>
+        <v>0.18</v>
       </c>
       <c r="G2">
-        <v>0.282703488372093</v>
+        <v>0.2575838926174497</v>
       </c>
       <c r="H2">
-        <v>0.282703488372093</v>
+        <v>0.2575838926174497</v>
       </c>
       <c r="I2">
-        <v>0.2359893889325057</v>
+        <v>0.3282338942147214</v>
       </c>
       <c r="J2">
-        <v>0.1667449045228939</v>
+        <v>0.2760401043661746</v>
       </c>
       <c r="K2">
-        <v>95.8</v>
+        <v>173.4</v>
       </c>
       <c r="L2">
-        <v>0.1392441860465116</v>
+        <v>0.232751677852349</v>
       </c>
       <c r="M2">
-        <v>40.2</v>
+        <v>31.6</v>
       </c>
       <c r="N2">
-        <v>0.02648395810000659</v>
+        <v>0.02548181598258205</v>
       </c>
       <c r="O2">
-        <v>0.4196242171189979</v>
+        <v>0.182237600922722</v>
       </c>
       <c r="P2">
-        <v>40.2</v>
+        <v>31.6</v>
       </c>
       <c r="Q2">
-        <v>0.02648395810000659</v>
+        <v>0.02548181598258205</v>
       </c>
       <c r="R2">
-        <v>0.4196242171189979</v>
+        <v>0.182237600922722</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>215.5</v>
+        <v>275.8</v>
       </c>
       <c r="V2">
-        <v>0.1419724619540154</v>
+        <v>0.2224014192403839</v>
       </c>
       <c r="W2">
-        <v>0.1226475483292792</v>
+        <v>0.2478559176672384</v>
       </c>
       <c r="X2">
-        <v>0.1642152879541893</v>
+        <v>0.1272700639899366</v>
       </c>
       <c r="Y2">
-        <v>-0.04156773962491012</v>
+        <v>0.1205858536773018</v>
       </c>
       <c r="Z2">
-        <v>0.9933848910800059</v>
+        <v>1.453236760348138</v>
       </c>
       <c r="AA2">
-        <v>0.1656418688176209</v>
+        <v>0.4011516269952615</v>
       </c>
       <c r="AB2">
-        <v>0.1629238276653961</v>
+        <v>0.12620314388485</v>
       </c>
       <c r="AC2">
-        <v>0.002718041152224765</v>
+        <v>0.2749484831104115</v>
       </c>
       <c r="AD2">
-        <v>28.4</v>
+        <v>26.7</v>
       </c>
       <c r="AE2">
-        <v>0.2815020721804781</v>
+        <v>0.148744050162609</v>
       </c>
       <c r="AF2">
-        <v>28.68150207218047</v>
+        <v>26.84874405016261</v>
       </c>
       <c r="AG2">
-        <v>-186.8184979278195</v>
+        <v>-248.9512559498374</v>
       </c>
       <c r="AH2">
-        <v>0.01854509577009145</v>
+        <v>0.02119165765485741</v>
       </c>
       <c r="AI2">
-        <v>0.03866048956884484</v>
+        <v>0.04363884414199401</v>
       </c>
       <c r="AJ2">
-        <v>-0.1403509083681105</v>
+        <v>-0.2511744654314346</v>
       </c>
       <c r="AK2">
-        <v>-0.3549108340478915</v>
+        <v>-0.7333986656702675</v>
       </c>
       <c r="AL2">
-        <v>33.8</v>
+        <v>40.6</v>
       </c>
       <c r="AM2">
-        <v>33.8</v>
+        <v>40.6</v>
       </c>
       <c r="AN2">
-        <v>0.1630150903757957</v>
+        <v>0.1071583374805349</v>
       </c>
       <c r="AO2">
-        <v>4.795857988165681</v>
+        <v>6.019704433497536</v>
       </c>
       <c r="AP2">
-        <v>-1.072332194492039</v>
+        <v>-0.9991461685871049</v>
       </c>
       <c r="AQ2">
-        <v>4.795857988165681</v>
+        <v>6.019704433497536</v>
       </c>
     </row>
     <row r="3">
@@ -722,46 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0761</v>
+        <v>0.092</v>
       </c>
       <c r="E3">
-        <v>0.0233</v>
+        <v>0.18</v>
       </c>
       <c r="G3">
-        <v>0.282703488372093</v>
+        <v>0.2575838926174497</v>
       </c>
       <c r="H3">
-        <v>0.282703488372093</v>
+        <v>0.2575838926174497</v>
       </c>
       <c r="I3">
-        <v>0.2359893889325057</v>
+        <v>0.3282338942147214</v>
       </c>
       <c r="J3">
-        <v>0.1667449045228939</v>
+        <v>0.2760401043661746</v>
       </c>
       <c r="K3">
-        <v>95.8</v>
+        <v>173.4</v>
       </c>
       <c r="L3">
-        <v>0.1392441860465116</v>
+        <v>0.232751677852349</v>
       </c>
       <c r="M3">
-        <v>40.2</v>
+        <v>31.6</v>
       </c>
       <c r="N3">
-        <v>0.02648395810000659</v>
+        <v>0.02548181598258205</v>
       </c>
       <c r="O3">
-        <v>0.4196242171189979</v>
+        <v>0.182237600922722</v>
       </c>
       <c r="P3">
-        <v>40.2</v>
+        <v>31.6</v>
       </c>
       <c r="Q3">
-        <v>0.02648395810000659</v>
+        <v>0.02548181598258205</v>
       </c>
       <c r="R3">
-        <v>0.4196242171189979</v>
+        <v>0.182237600922722</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,73 +770,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>215.5</v>
+        <v>275.8</v>
       </c>
       <c r="V3">
-        <v>0.1419724619540154</v>
+        <v>0.2224014192403839</v>
       </c>
       <c r="W3">
-        <v>0.1226475483292792</v>
+        <v>0.2478559176672384</v>
       </c>
       <c r="X3">
-        <v>0.1642152879541893</v>
+        <v>0.1272700639899366</v>
       </c>
       <c r="Y3">
-        <v>-0.04156773962491012</v>
+        <v>0.1205858536773018</v>
       </c>
       <c r="Z3">
-        <v>0.9933848910800059</v>
+        <v>1.453236760348138</v>
       </c>
       <c r="AA3">
-        <v>0.1656418688176209</v>
+        <v>0.4011516269952615</v>
       </c>
       <c r="AB3">
-        <v>0.1629238276653961</v>
+        <v>0.12620314388485</v>
       </c>
       <c r="AC3">
-        <v>0.002718041152224765</v>
+        <v>0.2749484831104115</v>
       </c>
       <c r="AD3">
-        <v>28.4</v>
+        <v>26.7</v>
       </c>
       <c r="AE3">
-        <v>0.2815020721804781</v>
+        <v>0.148744050162609</v>
       </c>
       <c r="AF3">
-        <v>28.68150207218047</v>
+        <v>26.84874405016261</v>
       </c>
       <c r="AG3">
-        <v>-186.8184979278195</v>
+        <v>-248.9512559498374</v>
       </c>
       <c r="AH3">
-        <v>0.01854509577009145</v>
+        <v>0.02119165765485741</v>
       </c>
       <c r="AI3">
-        <v>0.03866048956884484</v>
+        <v>0.04363884414199401</v>
       </c>
       <c r="AJ3">
-        <v>-0.1403509083681105</v>
+        <v>-0.2511744654314346</v>
       </c>
       <c r="AK3">
-        <v>-0.3549108340478915</v>
+        <v>-0.7333986656702675</v>
       </c>
       <c r="AL3">
-        <v>33.8</v>
+        <v>40.6</v>
       </c>
       <c r="AM3">
-        <v>33.8</v>
+        <v>40.6</v>
       </c>
       <c r="AN3">
-        <v>0.1630150903757957</v>
+        <v>0.1071583374805349</v>
       </c>
       <c r="AO3">
-        <v>4.795857988165681</v>
+        <v>6.019704433497536</v>
       </c>
       <c r="AP3">
-        <v>-1.072332194492039</v>
+        <v>-0.9991461685871049</v>
       </c>
       <c r="AQ3">
-        <v>4.795857988165681</v>
+        <v>6.019704433497536</v>
       </c>
     </row>
   </sheetData>
